--- a/static/data/exports/Retro_PY_GE_2024.xlsx
+++ b/static/data/exports/Retro_PY_GE_2024.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P196" t="n">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16829,7 +16829,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18241,7 +18241,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18466,7 +18466,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -19053,7 +19053,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19353,7 +19353,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23377,7 +23377,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23827,7 +23827,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24502,7 +24502,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24727,7 +24727,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25389,7 +25389,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25989,7 +25989,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26289,7 +26289,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26739,7 +26739,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26889,7 +26889,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27551,7 +27551,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27701,7 +27701,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27851,7 +27851,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -28001,7 +28001,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -28076,7 +28076,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28526,7 +28526,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P386" t="n">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29338,7 +29338,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29788,7 +29788,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29863,7 +29863,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -30013,7 +30013,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30388,7 +30388,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30463,7 +30463,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30613,7 +30613,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30688,7 +30688,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P408" t="n">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -31125,7 +31125,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31350,7 +31350,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31575,7 +31575,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -31650,7 +31650,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31725,7 +31725,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31800,7 +31800,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -31950,7 +31950,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -32250,7 +32250,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -32325,7 +32325,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32550,7 +32550,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32775,7 +32775,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32925,7 +32925,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -33137,7 +33137,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -33212,7 +33212,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -33287,7 +33287,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33362,7 +33362,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P443" t="n">
@@ -33512,7 +33512,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33587,7 +33587,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33662,7 +33662,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33812,7 +33812,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33887,7 +33887,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33962,7 +33962,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P451" t="n">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -34187,7 +34187,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -34262,7 +34262,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34487,7 +34487,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34562,7 +34562,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34712,7 +34712,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -34787,7 +34787,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P463" t="n">
@@ -35012,7 +35012,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35374,7 +35374,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35524,7 +35524,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35599,7 +35599,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35749,7 +35749,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -35824,7 +35824,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -35899,7 +35899,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35974,7 +35974,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -36049,7 +36049,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -36199,7 +36199,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -36349,7 +36349,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36424,7 +36424,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36499,7 +36499,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36649,7 +36649,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -36874,7 +36874,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -37024,7 +37024,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -37236,7 +37236,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -37311,7 +37311,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37386,7 +37386,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37461,7 +37461,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37536,7 +37536,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37611,7 +37611,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37686,7 +37686,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -37911,7 +37911,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -38061,7 +38061,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -38211,7 +38211,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -38286,7 +38286,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38436,7 +38436,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38511,7 +38511,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38586,7 +38586,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38811,7 +38811,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -38961,7 +38961,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -39036,7 +39036,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P520" t="n">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -39323,7 +39323,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39398,7 +39398,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39473,7 +39473,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39548,7 +39548,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P525" t="n">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39698,7 +39698,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39848,7 +39848,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39998,7 +39998,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -40073,7 +40073,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -40223,7 +40223,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -40298,7 +40298,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -40373,7 +40373,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40448,7 +40448,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40523,7 +40523,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40598,7 +40598,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40673,7 +40673,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -40898,7 +40898,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40973,7 +40973,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P544" t="n">
@@ -41048,7 +41048,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -41185,7 +41185,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41410,7 +41410,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41485,7 +41485,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41635,7 +41635,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41710,7 +41710,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P555" t="n">
@@ -41860,7 +41860,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -41935,7 +41935,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -42010,7 +42010,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -42085,7 +42085,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -42160,7 +42160,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -42235,7 +42235,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -42310,7 +42310,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -42385,7 +42385,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -42460,7 +42460,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42535,7 +42535,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42685,7 +42685,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -42760,7 +42760,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42910,7 +42910,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42985,7 +42985,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -43060,7 +43060,7 @@
       </c>
       <c r="O572" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P572" t="n">
@@ -43197,7 +43197,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -43272,7 +43272,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -43347,7 +43347,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43497,7 +43497,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P578" t="n">
@@ -43572,7 +43572,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43647,7 +43647,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -43722,7 +43722,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P581" t="n">
@@ -43797,7 +43797,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -43872,7 +43872,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P583" t="n">
@@ -43947,7 +43947,7 @@
       </c>
       <c r="O584" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P584" t="n">
@@ -44022,7 +44022,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P587" t="n">
@@ -44247,7 +44247,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -44322,7 +44322,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -44397,7 +44397,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P591" t="n">
@@ -44547,7 +44547,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P592" t="n">
@@ -44622,7 +44622,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44697,7 +44697,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P594" t="n">
@@ -44772,7 +44772,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -44847,7 +44847,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P596" t="n">
@@ -44922,7 +44922,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P597" t="n">
@@ -44997,7 +44997,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P598" t="n">
@@ -45072,7 +45072,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P599" t="n">
@@ -45209,7 +45209,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P601" t="n">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P602" t="n">
@@ -45359,7 +45359,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P603" t="n">
@@ -45434,7 +45434,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P604" t="n">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P605" t="n">
@@ -45584,7 +45584,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P606" t="n">
@@ -45659,7 +45659,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P607" t="n">
@@ -45734,7 +45734,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P608" t="n">
@@ -45809,7 +45809,7 @@
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P609" t="n">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="O610" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P610" t="n">
@@ -45959,7 +45959,7 @@
       </c>
       <c r="O611" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P611" t="n">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P612" t="n">
@@ -46109,7 +46109,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P613" t="n">
@@ -46184,7 +46184,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P614" t="n">
@@ -46259,7 +46259,7 @@
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P615" t="n">
@@ -46334,7 +46334,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P616" t="n">
@@ -46409,7 +46409,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P617" t="n">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P618" t="n">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P619" t="n">
@@ -46634,7 +46634,7 @@
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P620" t="n">
@@ -46709,7 +46709,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P621" t="n">
@@ -46784,7 +46784,7 @@
       </c>
       <c r="O622" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P622" t="n">
@@ -46859,7 +46859,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P623" t="n">
@@ -46934,7 +46934,7 @@
       </c>
       <c r="O624" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P624" t="n">
@@ -47009,7 +47009,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P625" t="n">
@@ -47084,7 +47084,7 @@
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P626" t="n">
@@ -47221,7 +47221,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P628" t="n">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P629" t="n">
@@ -47371,7 +47371,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P630" t="n">
@@ -47446,7 +47446,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P631" t="n">
@@ -47521,7 +47521,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P632" t="n">
@@ -47596,7 +47596,7 @@
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P633" t="n">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="O634" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P634" t="n">
@@ -47746,7 +47746,7 @@
       </c>
       <c r="O635" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P635" t="n">
@@ -47821,7 +47821,7 @@
       </c>
       <c r="O636" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P636" t="n">
@@ -47896,7 +47896,7 @@
       </c>
       <c r="O637" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P637" t="n">
@@ -47971,7 +47971,7 @@
       </c>
       <c r="O638" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P638" t="n">
@@ -48046,7 +48046,7 @@
       </c>
       <c r="O639" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P639" t="n">
@@ -48121,7 +48121,7 @@
       </c>
       <c r="O640" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P640" t="n">
@@ -48196,7 +48196,7 @@
       </c>
       <c r="O641" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P641" t="n">
@@ -48271,7 +48271,7 @@
       </c>
       <c r="O642" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P642" t="n">
@@ -48346,7 +48346,7 @@
       </c>
       <c r="O643" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P643" t="n">
@@ -48421,7 +48421,7 @@
       </c>
       <c r="O644" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P644" t="n">
@@ -48496,7 +48496,7 @@
       </c>
       <c r="O645" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P645" t="n">
@@ -48571,7 +48571,7 @@
       </c>
       <c r="O646" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P646" t="n">
@@ -48646,7 +48646,7 @@
       </c>
       <c r="O647" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P647" t="n">
@@ -48721,7 +48721,7 @@
       </c>
       <c r="O648" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P648" t="n">
@@ -48796,7 +48796,7 @@
       </c>
       <c r="O649" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P649" t="n">
@@ -48871,7 +48871,7 @@
       </c>
       <c r="O650" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P650" t="n">
@@ -48946,7 +48946,7 @@
       </c>
       <c r="O651" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P651" t="n">
@@ -49021,7 +49021,7 @@
       </c>
       <c r="O652" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P652" t="n">
@@ -49096,7 +49096,7 @@
       </c>
       <c r="O653" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P653" t="n">
@@ -49233,7 +49233,7 @@
       </c>
       <c r="O655" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P655" t="n">
@@ -49308,7 +49308,7 @@
       </c>
       <c r="O656" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P656" t="n">
@@ -49383,7 +49383,7 @@
       </c>
       <c r="O657" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P657" t="n">
@@ -49458,7 +49458,7 @@
       </c>
       <c r="O658" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P658" t="n">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="O659" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P659" t="n">
@@ -49608,7 +49608,7 @@
       </c>
       <c r="O660" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P660" t="n">
@@ -49683,7 +49683,7 @@
       </c>
       <c r="O661" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P661" t="n">
@@ -49758,7 +49758,7 @@
       </c>
       <c r="O662" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P662" t="n">
@@ -49833,7 +49833,7 @@
       </c>
       <c r="O663" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P663" t="n">
@@ -49908,7 +49908,7 @@
       </c>
       <c r="O664" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P664" t="n">
@@ -49983,7 +49983,7 @@
       </c>
       <c r="O665" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P665" t="n">
@@ -50058,7 +50058,7 @@
       </c>
       <c r="O666" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P666" t="n">
@@ -50133,7 +50133,7 @@
       </c>
       <c r="O667" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P667" t="n">
@@ -50208,7 +50208,7 @@
       </c>
       <c r="O668" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P668" t="n">
@@ -50283,7 +50283,7 @@
       </c>
       <c r="O669" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P669" t="n">
@@ -50358,7 +50358,7 @@
       </c>
       <c r="O670" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P670" t="n">
@@ -50433,7 +50433,7 @@
       </c>
       <c r="O671" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P671" t="n">
@@ -50508,7 +50508,7 @@
       </c>
       <c r="O672" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P672" t="n">
@@ -50583,7 +50583,7 @@
       </c>
       <c r="O673" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P673" t="n">
@@ -50658,7 +50658,7 @@
       </c>
       <c r="O674" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P674" t="n">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="O675" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P675" t="n">
@@ -50808,7 +50808,7 @@
       </c>
       <c r="O676" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P676" t="n">
@@ -50883,7 +50883,7 @@
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P677" t="n">
@@ -50958,7 +50958,7 @@
       </c>
       <c r="O678" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P678" t="n">
@@ -51033,7 +51033,7 @@
       </c>
       <c r="O679" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P679" t="n">
@@ -51108,7 +51108,7 @@
       </c>
       <c r="O680" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P680" t="n">
@@ -51245,7 +51245,7 @@
       </c>
       <c r="O682" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P682" t="n">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="O683" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P683" t="n">
@@ -51395,7 +51395,7 @@
       </c>
       <c r="O684" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P684" t="n">
@@ -51470,7 +51470,7 @@
       </c>
       <c r="O685" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P685" t="n">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="O686" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P686" t="n">
@@ -51620,7 +51620,7 @@
       </c>
       <c r="O687" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P687" t="n">
@@ -51695,7 +51695,7 @@
       </c>
       <c r="O688" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P688" t="n">
@@ -51770,7 +51770,7 @@
       </c>
       <c r="O689" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P689" t="n">
@@ -51845,7 +51845,7 @@
       </c>
       <c r="O690" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P690" t="n">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="O691" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P691" t="n">
@@ -51995,7 +51995,7 @@
       </c>
       <c r="O692" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P692" t="n">
@@ -52070,7 +52070,7 @@
       </c>
       <c r="O693" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P693" t="n">
@@ -52145,7 +52145,7 @@
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P694" t="n">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P695" t="n">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="O696" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P696" t="n">
@@ -52370,7 +52370,7 @@
       </c>
       <c r="O697" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P697" t="n">
@@ -52445,7 +52445,7 @@
       </c>
       <c r="O698" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P698" t="n">
@@ -52520,7 +52520,7 @@
       </c>
       <c r="O699" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P699" t="n">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="O700" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P700" t="n">
@@ -52670,7 +52670,7 @@
       </c>
       <c r="O701" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P701" t="n">
@@ -52745,7 +52745,7 @@
       </c>
       <c r="O702" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P702" t="n">
@@ -52820,7 +52820,7 @@
       </c>
       <c r="O703" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P703" t="n">
@@ -52895,7 +52895,7 @@
       </c>
       <c r="O704" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P704" t="n">
@@ -52970,7 +52970,7 @@
       </c>
       <c r="O705" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P705" t="n">
@@ -53045,7 +53045,7 @@
       </c>
       <c r="O706" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P706" t="n">
@@ -53120,7 +53120,7 @@
       </c>
       <c r="O707" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P707" t="n">
@@ -53257,7 +53257,7 @@
       </c>
       <c r="O709" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P709" t="n">
@@ -53332,7 +53332,7 @@
       </c>
       <c r="O710" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P710" t="n">
@@ -53407,7 +53407,7 @@
       </c>
       <c r="O711" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P711" t="n">
@@ -53482,7 +53482,7 @@
       </c>
       <c r="O712" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P712" t="n">
@@ -53557,7 +53557,7 @@
       </c>
       <c r="O713" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P713" t="n">
@@ -53632,7 +53632,7 @@
       </c>
       <c r="O714" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P714" t="n">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="O715" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P715" t="n">
@@ -53782,7 +53782,7 @@
       </c>
       <c r="O716" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P716" t="n">
@@ -53857,7 +53857,7 @@
       </c>
       <c r="O717" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P717" t="n">
@@ -53932,7 +53932,7 @@
       </c>
       <c r="O718" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P718" t="n">
@@ -54007,7 +54007,7 @@
       </c>
       <c r="O719" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P719" t="n">
@@ -54082,7 +54082,7 @@
       </c>
       <c r="O720" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P720" t="n">
@@ -54157,7 +54157,7 @@
       </c>
       <c r="O721" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P721" t="n">
@@ -54232,7 +54232,7 @@
       </c>
       <c r="O722" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P722" t="n">
@@ -54307,7 +54307,7 @@
       </c>
       <c r="O723" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P723" t="n">
@@ -54382,7 +54382,7 @@
       </c>
       <c r="O724" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P724" t="n">
@@ -54457,7 +54457,7 @@
       </c>
       <c r="O725" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P725" t="n">
@@ -54532,7 +54532,7 @@
       </c>
       <c r="O726" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P726" t="n">
@@ -54607,7 +54607,7 @@
       </c>
       <c r="O727" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P727" t="n">
@@ -54682,7 +54682,7 @@
       </c>
       <c r="O728" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P728" t="n">
@@ -54757,7 +54757,7 @@
       </c>
       <c r="O729" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P729" t="n">
@@ -54832,7 +54832,7 @@
       </c>
       <c r="O730" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P730" t="n">
@@ -54907,7 +54907,7 @@
       </c>
       <c r="O731" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P731" t="n">
@@ -54982,7 +54982,7 @@
       </c>
       <c r="O732" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P732" t="n">
@@ -55057,7 +55057,7 @@
       </c>
       <c r="O733" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P733" t="n">
@@ -55132,7 +55132,7 @@
       </c>
       <c r="O734" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P734" t="n">
@@ -55269,7 +55269,7 @@
       </c>
       <c r="O736" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P736" t="n">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P737" t="n">
@@ -55419,7 +55419,7 @@
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P738" t="n">
@@ -55494,7 +55494,7 @@
       </c>
       <c r="O739" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P739" t="n">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="O740" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P740" t="n">
@@ -55644,7 +55644,7 @@
       </c>
       <c r="O741" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P741" t="n">
@@ -55719,7 +55719,7 @@
       </c>
       <c r="O742" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P742" t="n">
@@ -55794,7 +55794,7 @@
       </c>
       <c r="O743" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P743" t="n">
@@ -55869,7 +55869,7 @@
       </c>
       <c r="O744" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P744" t="n">
@@ -55944,7 +55944,7 @@
       </c>
       <c r="O745" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P745" t="n">
@@ -56019,7 +56019,7 @@
       </c>
       <c r="O746" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P746" t="n">
@@ -56094,7 +56094,7 @@
       </c>
       <c r="O747" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P747" t="n">
@@ -56169,7 +56169,7 @@
       </c>
       <c r="O748" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P748" t="n">
@@ -56244,7 +56244,7 @@
       </c>
       <c r="O749" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P749" t="n">
@@ -56319,7 +56319,7 @@
       </c>
       <c r="O750" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P750" t="n">
@@ -56394,7 +56394,7 @@
       </c>
       <c r="O751" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P751" t="n">
@@ -56469,7 +56469,7 @@
       </c>
       <c r="O752" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P752" t="n">
@@ -56544,7 +56544,7 @@
       </c>
       <c r="O753" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P753" t="n">
@@ -56619,7 +56619,7 @@
       </c>
       <c r="O754" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P754" t="n">
@@ -56694,7 +56694,7 @@
       </c>
       <c r="O755" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P755" t="n">
@@ -56769,7 +56769,7 @@
       </c>
       <c r="O756" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P756" t="n">
@@ -56844,7 +56844,7 @@
       </c>
       <c r="O757" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P757" t="n">
@@ -56919,7 +56919,7 @@
       </c>
       <c r="O758" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P758" t="n">
@@ -56994,7 +56994,7 @@
       </c>
       <c r="O759" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P759" t="n">
@@ -57069,7 +57069,7 @@
       </c>
       <c r="O760" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P760" t="n">
@@ -57206,7 +57206,7 @@
       </c>
       <c r="O762" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P762" t="n">
@@ -57281,7 +57281,7 @@
       </c>
       <c r="O763" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P763" t="n">
@@ -57356,7 +57356,7 @@
       </c>
       <c r="O764" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P764" t="n">
@@ -57431,7 +57431,7 @@
       </c>
       <c r="O765" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P765" t="n">
@@ -57506,7 +57506,7 @@
       </c>
       <c r="O766" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P766" t="n">
@@ -57581,7 +57581,7 @@
       </c>
       <c r="O767" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P767" t="n">
@@ -57656,7 +57656,7 @@
       </c>
       <c r="O768" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P768" t="n">
@@ -57731,7 +57731,7 @@
       </c>
       <c r="O769" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P769" t="n">
@@ -57806,7 +57806,7 @@
       </c>
       <c r="O770" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P770" t="n">
@@ -57881,7 +57881,7 @@
       </c>
       <c r="O771" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P771" t="n">
@@ -57956,7 +57956,7 @@
       </c>
       <c r="O772" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P772" t="n">
@@ -58031,7 +58031,7 @@
       </c>
       <c r="O773" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P773" t="n">
@@ -58106,7 +58106,7 @@
       </c>
       <c r="O774" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P774" t="n">
@@ -58181,7 +58181,7 @@
       </c>
       <c r="O775" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P775" t="n">
@@ -58256,7 +58256,7 @@
       </c>
       <c r="O776" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P776" t="n">
@@ -58331,7 +58331,7 @@
       </c>
       <c r="O777" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P777" t="n">
@@ -58406,7 +58406,7 @@
       </c>
       <c r="O778" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P778" t="n">
@@ -58481,7 +58481,7 @@
       </c>
       <c r="O779" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P779" t="n">
@@ -58556,7 +58556,7 @@
       </c>
       <c r="O780" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P780" t="n">
@@ -58631,7 +58631,7 @@
       </c>
       <c r="O781" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P781" t="n">
@@ -58706,7 +58706,7 @@
       </c>
       <c r="O782" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P782" t="n">
@@ -58781,7 +58781,7 @@
       </c>
       <c r="O783" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P783" t="n">
@@ -58856,7 +58856,7 @@
       </c>
       <c r="O784" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P784" t="n">
@@ -58931,7 +58931,7 @@
       </c>
       <c r="O785" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P785" t="n">
@@ -59006,7 +59006,7 @@
       </c>
       <c r="O786" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P786" t="n">
@@ -59143,7 +59143,7 @@
       </c>
       <c r="O788" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P788" t="n">
@@ -59218,7 +59218,7 @@
       </c>
       <c r="O789" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P789" t="n">
@@ -59293,7 +59293,7 @@
       </c>
       <c r="O790" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P790" t="n">
@@ -59368,7 +59368,7 @@
       </c>
       <c r="O791" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P791" t="n">
@@ -59443,7 +59443,7 @@
       </c>
       <c r="O792" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P792" t="n">
@@ -59518,7 +59518,7 @@
       </c>
       <c r="O793" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P793" t="n">
@@ -59593,7 +59593,7 @@
       </c>
       <c r="O794" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P794" t="n">
@@ -59668,7 +59668,7 @@
       </c>
       <c r="O795" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P795" t="n">
@@ -59743,7 +59743,7 @@
       </c>
       <c r="O796" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P796" t="n">
@@ -59818,7 +59818,7 @@
       </c>
       <c r="O797" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P797" t="n">
@@ -59893,7 +59893,7 @@
       </c>
       <c r="O798" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P798" t="n">
@@ -59968,7 +59968,7 @@
       </c>
       <c r="O799" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P799" t="n">
@@ -60043,7 +60043,7 @@
       </c>
       <c r="O800" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P800" t="n">
@@ -60118,7 +60118,7 @@
       </c>
       <c r="O801" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P801" t="n">
@@ -60193,7 +60193,7 @@
       </c>
       <c r="O802" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P802" t="n">
@@ -60268,7 +60268,7 @@
       </c>
       <c r="O803" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P803" t="n">
@@ -60343,7 +60343,7 @@
       </c>
       <c r="O804" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P804" t="n">
@@ -60418,7 +60418,7 @@
       </c>
       <c r="O805" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P805" t="n">
@@ -60493,7 +60493,7 @@
       </c>
       <c r="O806" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P806" t="n">
@@ -60568,7 +60568,7 @@
       </c>
       <c r="O807" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P807" t="n">
@@ -60643,7 +60643,7 @@
       </c>
       <c r="O808" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P808" t="n">
@@ -60718,7 +60718,7 @@
       </c>
       <c r="O809" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P809" t="n">
@@ -60793,7 +60793,7 @@
       </c>
       <c r="O810" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P810" t="n">
@@ -60868,7 +60868,7 @@
       </c>
       <c r="O811" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P811" t="n">
